--- a/DigSite/New Arcaism/uarm 2026 b/maestr/Lista de temas de los estudiantes.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 b/maestr/Lista de temas de los estudiantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 b\maestr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F0E60C-9FD0-4FB0-B3D1-938BAFCD1F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE90FCDC-1A86-4711-8C94-6188023D8438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6225" yWindow="0" windowWidth="14235" windowHeight="10920" xr2:uid="{3CB789E7-1C2F-4AA2-AAD4-CECAAC230C96}"/>
+    <workbookView xWindow="6225" yWindow="0" windowWidth="14175" windowHeight="10920" xr2:uid="{3CB789E7-1C2F-4AA2-AAD4-CECAAC230C96}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t xml:space="preserve"> N° </t>
   </si>
@@ -226,6 +226,18 @@
   </si>
   <si>
     <t>Martes 25 Agosto</t>
+  </si>
+  <si>
+    <t>Sábado 29 Agosto</t>
+  </si>
+  <si>
+    <t>Lunes 31 Agosto</t>
+  </si>
+  <si>
+    <t>revisar textos de Arendt, encontrar un puente entre los dos ejes de los temas sugeridos; responsabildiad moral desde la creación de la IA y el tema del mal banal. Le recomiendo un par de textos de Arendt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asesor, trámites, burocracias, no le quedan claro. Habermas y la teoría deliberativa + procedimiento del derecho concursal. Le recomiendo una lectura de Habermas. Necesita centrarse en el aspecto filosófico, le he compartido 4 lecturas, una de ellas precisa para su tema. Ha cambiado lo que tenía avanzado, según me dice. </t>
   </si>
 </sst>
 </file>
@@ -632,16 +644,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C68ADC-CBC3-4A1D-B92D-52EEC4DA6302}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -657,8 +671,14 @@
       <c r="E1" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -669,7 +689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -680,7 +700,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -690,8 +710,11 @@
       <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -702,7 +725,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -713,7 +736,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -724,7 +747,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -735,7 +758,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -746,7 +769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -757,7 +780,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -768,7 +791,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -779,7 +802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -790,7 +813,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -801,7 +824,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -812,7 +835,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -823,7 +846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -834,7 +857,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -845,7 +868,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -856,7 +879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -867,7 +890,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -877,8 +900,11 @@
       <c r="C21" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -889,7 +915,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -900,7 +926,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -911,7 +937,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -922,7 +948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -933,7 +959,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -944,7 +970,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -955,7 +981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -966,7 +992,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -977,7 +1003,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>

--- a/DigSite/New Arcaism/uarm 2026 b/maestr/Lista de temas de los estudiantes.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 b/maestr/Lista de temas de los estudiantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 b\maestr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE90FCDC-1A86-4711-8C94-6188023D8438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B1CFA5-269B-46A2-B42C-67CA97A06A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6225" yWindow="0" windowWidth="14175" windowHeight="10920" xr2:uid="{3CB789E7-1C2F-4AA2-AAD4-CECAAC230C96}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3CB789E7-1C2F-4AA2-AAD4-CECAAC230C96}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t xml:space="preserve"> N° </t>
   </si>
@@ -238,6 +238,27 @@
   </si>
   <si>
     <t xml:space="preserve">Asesor, trámites, burocracias, no le quedan claro. Habermas y la teoría deliberativa + procedimiento del derecho concursal. Le recomiendo una lectura de Habermas. Necesita centrarse en el aspecto filosófico, le he compartido 4 lecturas, una de ellas precisa para su tema. Ha cambiado lo que tenía avanzado, según me dice. </t>
+  </si>
+  <si>
+    <t>martes 1</t>
+  </si>
+  <si>
+    <t>sabado 5</t>
+  </si>
+  <si>
+    <t>sabado 12</t>
+  </si>
+  <si>
+    <t>lunes 7</t>
+  </si>
+  <si>
+    <t>martes 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">polarización y fragmentación de opinión pública; es afectiva, no deliberativa. Redes sociales tienen poco espacio para reflexion. Han y Habermas. Le recomiendo taylor, etica de la autenticidad, y puntualizar el modo en que los algoritmos funcionan a intereses económicos. Le comparto tmb textos de Habermas y le comento sobre un diálogo con K O Appel. </t>
+  </si>
+  <si>
+    <t>perdió todo su trabajo -.-, libertad negativa y positiva, interna y externa. Tiene problemas con el curso de críticos de la modernidad, dice que va a descargar todo y empezar de nuevo con lo que pueda recuperar. No pudimos hablar mucho de su tema porque claramente está desalentado.</t>
   </si>
 </sst>
 </file>
@@ -644,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C68ADC-CBC3-4A1D-B92D-52EEC4DA6302}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
@@ -652,10 +673,11 @@
     <col min="4" max="4" width="24.140625" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -677,8 +699,23 @@
       <c r="G1" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -689,7 +726,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -700,7 +737,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -714,7 +751,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -725,7 +762,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -736,7 +773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -747,7 +784,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -758,7 +795,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -769,7 +806,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -780,7 +817,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -791,7 +828,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -802,7 +839,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -813,7 +850,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -823,8 +860,11 @@
       <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="L14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -835,7 +875,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -846,7 +886,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -857,7 +897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -868,7 +908,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -879,7 +919,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -890,7 +930,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -904,7 +944,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -915,7 +955,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -926,7 +966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -937,7 +977,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -948,7 +988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -959,7 +999,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -970,7 +1010,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -981,7 +1021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -991,8 +1031,11 @@
       <c r="C29" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="L29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1003,7 +1046,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
